--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>65:00</t>
+          <t>30:01</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -1531,10 +1531,10 @@
         <v>15</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>46:01</t>
+          <t>31:01</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42:14</t>
+          <t>22:14</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>23</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>5</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25:34</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -2511,16 +2511,16 @@
         <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>43:11</t>
+          <t>28:11</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -2707,16 +2707,16 @@
         <v>25</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>5</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>73:05</t>
+          <t>28:06</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>26:39</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>45:07</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>25.8%</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
           <t>8.7%</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>130</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>6</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>29:07</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -4488,10 +4488,10 @@
         <v>26</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>78:38</t>
+          <t>33:39</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>7</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>71:00</t>
+          <t>36:01</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>39:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>62:12</t>
+          <t>27:13</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
         <v>17</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>45:26</t>
+          <t>30:27</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>15</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>39:45</t>
+          <t>29:46</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6252,16 +6252,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>38:44</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>126</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1531,10 +1531,10 @@
         <v>15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2315,16 +2315,16 @@
         <v>23</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>5</v>
@@ -2511,16 +2511,16 @@
         <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2707,16 +2707,16 @@
         <v>25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
         <v>5</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>3</v>
@@ -3827,16 +3827,16 @@
         <v>130</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>6</v>
@@ -4488,10 +4488,10 @@
         <v>26</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>7</v>
@@ -4880,7 +4880,7 @@
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>17</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>15</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
         <v>3</v>
       </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>126</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_391_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -695,17 +695,17 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V2" t="n">
         <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -851,20 +851,20 @@
         <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
         <v>4</v>
       </c>
-      <c r="Y18" t="n">
-        <v>5</v>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1935,10 +1935,10 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2363,22 +2363,22 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
         <v>3</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>4</v>
-      </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
         <v>5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>7</v>
-      </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>12</v>
       </c>
       <c r="AK30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4533,25 +4533,25 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,10 +5284,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
